--- a/diseases/d192/2010-2014.xlsx
+++ b/diseases/d192/2010-2014.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16448,7 +16448,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18032,7 +18032,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">

--- a/diseases/d192/2010-2014.xlsx
+++ b/diseases/d192/2010-2014.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16448,7 +16448,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18032,7 +18032,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">

--- a/diseases/d192/2010-2014.xlsx
+++ b/diseases/d192/2010-2014.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16448,7 +16448,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18032,7 +18032,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">

--- a/diseases/d192/2010-2014.xlsx
+++ b/diseases/d192/2010-2014.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16448,7 +16448,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18032,7 +18032,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">

--- a/diseases/d192/2010-2014.xlsx
+++ b/diseases/d192/2010-2014.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16448,7 +16448,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18032,7 +18032,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">

--- a/diseases/d192/2010-2014.xlsx
+++ b/diseases/d192/2010-2014.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16448,7 +16448,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18032,7 +18032,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
